--- a/STP/presentations/Survey/survey_P.xlsx
+++ b/STP/presentations/Survey/survey_P.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samue\Documents\trainings\STP\presentations\Survey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E123F1-1D04-4F40-A21C-6A58B04A90C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC93692D-0B54-4296-B0F6-636239CFE230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F372B3D-94CE-0641-986A-C67A94B167DA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="33">
   <si>
     <t>Infrastructure</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>participant_24</t>
+  </si>
+  <si>
+    <t>question_number</t>
   </si>
 </sst>
 </file>
@@ -509,10 +512,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9071694-338F-9C4E-BE66-780AC1D3A6E8}">
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -520,79 +523,82 @@
         <v>7</v>
       </c>
       <c r="C1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>14</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>15</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>16</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>17</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>18</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>19</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>20</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>22</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>23</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>24</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>25</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>26</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>27</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>28</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>29</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>30</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -600,79 +606,82 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>5</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O2">
         <v>4</v>
       </c>
       <c r="P2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q2">
         <v>5</v>
       </c>
       <c r="R2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T2">
         <v>5</v>
       </c>
       <c r="U2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y2">
         <v>5</v>
       </c>
       <c r="Z2">
+        <v>5</v>
+      </c>
+      <c r="AA2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -680,13 +689,13 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -701,22 +710,22 @@
         <v>5</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>5</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N3">
         <v>4</v>
       </c>
       <c r="O3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P3">
         <v>5</v>
@@ -734,10 +743,10 @@
         <v>5</v>
       </c>
       <c r="U3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W3">
         <v>5</v>
@@ -749,10 +758,13 @@
         <v>5</v>
       </c>
       <c r="Z3">
+        <v>5</v>
+      </c>
+      <c r="AA3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -760,46 +772,46 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H4">
         <v>5</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>5</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>3</v>
       </c>
       <c r="O4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -811,10 +823,10 @@
         <v>4</v>
       </c>
       <c r="T4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V4">
         <v>5</v>
@@ -829,10 +841,13 @@
         <v>5</v>
       </c>
       <c r="Z4">
+        <v>5</v>
+      </c>
+      <c r="AA4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -840,25 +855,25 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <v>5</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5">
         <v>5</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -876,43 +891,46 @@
         <v>4</v>
       </c>
       <c r="O5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S5">
+        <v>4</v>
+      </c>
+      <c r="T5">
         <v>2</v>
       </c>
-      <c r="T5">
-        <v>5</v>
-      </c>
       <c r="U5">
         <v>5</v>
       </c>
       <c r="V5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X5">
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z5">
+        <v>4</v>
+      </c>
+      <c r="AA5">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -920,34 +938,34 @@
         <v>4</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6">
         <v>4</v>
@@ -962,25 +980,25 @@
         <v>4</v>
       </c>
       <c r="Q6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S6">
         <v>1</v>
       </c>
       <c r="T6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U6">
         <v>2</v>
       </c>
       <c r="V6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X6">
         <v>5</v>
@@ -989,10 +1007,13 @@
         <v>5</v>
       </c>
       <c r="Z6">
+        <v>5</v>
+      </c>
+      <c r="AA6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -1000,7 +1021,7 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -1024,10 +1045,10 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M7">
         <v>4</v>
@@ -1036,19 +1057,19 @@
         <v>4</v>
       </c>
       <c r="O7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7">
         <v>5</v>
@@ -1066,13 +1087,16 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z7">
+        <v>4</v>
+      </c>
+      <c r="AA7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -1080,34 +1104,34 @@
         <v>4</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K8">
         <v>5</v>
       </c>
       <c r="L8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M8">
         <v>4</v>
@@ -1119,40 +1143,43 @@
         <v>4</v>
       </c>
       <c r="P8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q8">
         <v>5</v>
       </c>
       <c r="R8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y8">
         <v>5</v>
       </c>
       <c r="Z8">
+        <v>5</v>
+      </c>
+      <c r="AA8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -1160,7 +1187,7 @@
         <v>5</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>5</v>
@@ -1169,61 +1196,61 @@
         <v>5</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I9">
         <v>5</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>3</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O9">
         <v>5</v>
       </c>
       <c r="P9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R9">
+        <v>5</v>
+      </c>
+      <c r="S9">
         <v>2</v>
       </c>
-      <c r="S9">
-        <v>4</v>
-      </c>
       <c r="T9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y9">
         <v>5</v>
@@ -1231,8 +1258,11 @@
       <c r="Z9">
         <v>5</v>
       </c>
+      <c r="AA9">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -1240,16 +1270,16 @@
         <v>4</v>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>5</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -1264,35 +1294,35 @@
         <v>5</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>4</v>
       </c>
       <c r="O10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
         <v>2</v>
       </c>
-      <c r="T10">
-        <v>5</v>
-      </c>
       <c r="U10">
         <v>5</v>
       </c>
@@ -1311,8 +1341,11 @@
       <c r="Z10">
         <v>5</v>
       </c>
+      <c r="AA10">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -1320,7 +1353,7 @@
         <v>4</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -1338,25 +1371,25 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K11">
         <v>5</v>
       </c>
       <c r="L11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>4</v>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P11">
         <v>5</v>
@@ -1365,13 +1398,13 @@
         <v>5</v>
       </c>
       <c r="R11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S11">
         <v>3</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U11">
         <v>5</v>
@@ -1391,8 +1424,11 @@
       <c r="Z11">
         <v>5</v>
       </c>
+      <c r="AA11">
+        <v>5</v>
+      </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -1400,7 +1436,7 @@
         <v>4</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -1418,11 +1454,11 @@
         <v>5</v>
       </c>
       <c r="I12">
+        <v>5</v>
+      </c>
+      <c r="J12">
         <v>2</v>
       </c>
-      <c r="J12">
-        <v>5</v>
-      </c>
       <c r="K12">
         <v>5</v>
       </c>
@@ -1430,13 +1466,13 @@
         <v>5</v>
       </c>
       <c r="M12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>4</v>
       </c>
       <c r="O12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P12">
         <v>5</v>
@@ -1445,16 +1481,16 @@
         <v>5</v>
       </c>
       <c r="R12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V12">
         <v>5</v>
@@ -1471,8 +1507,11 @@
       <c r="Z12">
         <v>5</v>
       </c>
+      <c r="AA12">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -1480,7 +1519,7 @@
         <v>4</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -1498,41 +1537,41 @@
         <v>5</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>4</v>
       </c>
       <c r="M13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S13">
+        <v>4</v>
+      </c>
+      <c r="T13">
         <v>2</v>
       </c>
-      <c r="T13">
-        <v>4</v>
-      </c>
       <c r="U13">
         <v>4</v>
       </c>
@@ -1540,19 +1579,22 @@
         <v>4</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X13">
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z13">
+        <v>3</v>
+      </c>
+      <c r="AA13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -1560,79 +1602,82 @@
         <v>4</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14">
         <v>2</v>
       </c>
-      <c r="E14">
-        <v>5</v>
-      </c>
       <c r="F14">
         <v>5</v>
       </c>
       <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="H14">
         <v>2</v>
       </c>
-      <c r="H14">
-        <v>5</v>
-      </c>
       <c r="I14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L14">
         <v>5</v>
       </c>
       <c r="M14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O14">
         <v>5</v>
       </c>
       <c r="P14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z14">
+        <v>3</v>
+      </c>
+      <c r="AA14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>2</v>
       </c>
@@ -1640,37 +1685,37 @@
         <v>4</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D15">
         <v>5</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F15">
         <v>4</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15">
         <v>5</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>4</v>
@@ -1682,13 +1727,13 @@
         <v>4</v>
       </c>
       <c r="Q15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T15">
         <v>5</v>
@@ -1697,10 +1742,10 @@
         <v>5</v>
       </c>
       <c r="V15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1711,8 +1756,11 @@
       <c r="Z15">
         <v>5</v>
       </c>
+      <c r="AA15">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -1720,7 +1768,7 @@
         <v>4</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D16">
         <v>5</v>
@@ -1729,46 +1777,46 @@
         <v>5</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16">
         <v>5</v>
       </c>
       <c r="I16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L16">
         <v>5</v>
       </c>
       <c r="M16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>4</v>
       </c>
       <c r="O16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R16">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16">
         <v>5</v>
@@ -1786,13 +1834,16 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z16">
+        <v>1</v>
+      </c>
+      <c r="AA16">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -1800,7 +1851,7 @@
         <v>4</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D17">
         <v>4</v>
@@ -1809,22 +1860,22 @@
         <v>4</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>1</v>
       </c>
       <c r="K17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L17">
         <v>4</v>
@@ -1833,19 +1884,19 @@
         <v>4</v>
       </c>
       <c r="N17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S17">
         <v>1</v>
@@ -1854,25 +1905,28 @@
         <v>1</v>
       </c>
       <c r="U17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X17">
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z17">
+        <v>3</v>
+      </c>
+      <c r="AA17">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -1880,7 +1934,7 @@
         <v>5</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D18">
         <v>5</v>
@@ -1892,10 +1946,10 @@
         <v>5</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I18">
         <v>5</v>
@@ -1910,13 +1964,13 @@
         <v>5</v>
       </c>
       <c r="M18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P18">
         <v>5</v>
@@ -1925,34 +1979,37 @@
         <v>5</v>
       </c>
       <c r="R18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z18">
+        <v>4</v>
+      </c>
+      <c r="AA18">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1960,7 +2017,7 @@
         <v>5</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -1972,31 +2029,31 @@
         <v>5</v>
       </c>
       <c r="G19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I19">
         <v>5</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L19">
         <v>5</v>
       </c>
       <c r="M19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P19">
         <v>5</v>
@@ -2005,16 +2062,16 @@
         <v>5</v>
       </c>
       <c r="R19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -2029,6 +2086,9 @@
         <v>5</v>
       </c>
       <c r="Z19">
+        <v>5</v>
+      </c>
+      <c r="AA19">
         <v>3</v>
       </c>
     </row>

--- a/STP/presentations/Survey/survey_P.xlsx
+++ b/STP/presentations/Survey/survey_P.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samue\Documents\trainings\STP\presentations\Survey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC93692D-0B54-4296-B0F6-636239CFE230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3800064-FD73-48ED-96A0-2AD7A2D59B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F372B3D-94CE-0641-986A-C67A94B167DA}"/>
   </bookViews>
